--- a/notebooks/aggregated_df_experiments.xlsx
+++ b/notebooks/aggregated_df_experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectFiles\nlp_lab\notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49491283-9E4E-4C51-9E86-85C5794144CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F73AD9E-7F3F-445F-BB1E-1F8C23315DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B8073DA7-9012-41FF-B31F-E4DF912A8E0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92B4B975-10AE-4881-A687-E266A22D57E7}"/>
   </bookViews>
   <sheets>
     <sheet name="aggregated_df_experiments" sheetId="1" r:id="rId1"/>
@@ -945,14 +945,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014182E0-0F64-41E4-8B38-D14BA84013E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E296F0-887D-4CA4-B8F9-FCCD8573A670}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:F865"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1072,7 +1074,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1192,7 +1194,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1312,7 +1314,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1432,7 +1434,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1552,7 +1554,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1672,7 +1674,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1792,7 +1794,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1829,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -1849,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="F45">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -1869,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -1889,7 +1891,7 @@
         <v>15</v>
       </c>
       <c r="F47">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -1909,10 +1911,10 @@
         <v>20</v>
       </c>
       <c r="F48">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1929,7 +1931,7 @@
         <v>25</v>
       </c>
       <c r="F49">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -2032,7 +2034,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2152,7 +2154,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2272,7 +2274,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2392,7 +2394,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2512,7 +2514,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2632,7 +2634,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2752,7 +2754,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
@@ -2872,7 +2874,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2992,7 +2994,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
@@ -3112,7 +3114,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
@@ -3149,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3169,7 +3171,7 @@
         <v>5</v>
       </c>
       <c r="F111">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3189,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3209,7 +3211,7 @@
         <v>15</v>
       </c>
       <c r="F113">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3229,7 +3231,7 @@
         <v>20</v>
       </c>
       <c r="F114">
-        <v>1219</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3249,7 +3251,7 @@
         <v>25</v>
       </c>
       <c r="F115">
-        <v>1219</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3269,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="F116">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3289,7 +3291,7 @@
         <v>5</v>
       </c>
       <c r="F117">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3309,7 +3311,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3329,7 +3331,7 @@
         <v>15</v>
       </c>
       <c r="F119">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3349,10 +3351,10 @@
         <v>20</v>
       </c>
       <c r="F120">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
@@ -3369,7 +3371,7 @@
         <v>25</v>
       </c>
       <c r="F121">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3389,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="F122">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3409,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="F123">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3429,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3449,7 +3451,7 @@
         <v>15</v>
       </c>
       <c r="F125">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3469,10 +3471,10 @@
         <v>20</v>
       </c>
       <c r="F126">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>125</v>
       </c>
@@ -3489,7 +3491,7 @@
         <v>25</v>
       </c>
       <c r="F127">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3509,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="F128">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3529,7 +3531,7 @@
         <v>5</v>
       </c>
       <c r="F129">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3549,7 +3551,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3569,7 +3571,7 @@
         <v>15</v>
       </c>
       <c r="F131">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3589,10 +3591,10 @@
         <v>20</v>
       </c>
       <c r="F132">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>131</v>
       </c>
@@ -3609,7 +3611,7 @@
         <v>25</v>
       </c>
       <c r="F133">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -3712,7 +3714,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>137</v>
       </c>
@@ -3832,7 +3834,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>143</v>
       </c>
@@ -3852,7 +3854,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>144</v>
       </c>
@@ -3989,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="F152">
-        <v>1119</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4009,7 +4011,7 @@
         <v>5</v>
       </c>
       <c r="F153">
-        <v>1119</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4029,7 +4031,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>1119</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4049,7 +4051,7 @@
         <v>15</v>
       </c>
       <c r="F155">
-        <v>1119</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4069,10 +4071,10 @@
         <v>20</v>
       </c>
       <c r="F156">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>155</v>
       </c>
@@ -4089,7 +4091,7 @@
         <v>25</v>
       </c>
       <c r="F157">
-        <v>1119</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4192,7 +4194,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>161</v>
       </c>
@@ -4212,7 +4214,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>162</v>
       </c>
@@ -4432,7 +4434,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>173</v>
       </c>
@@ -4552,7 +4554,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>179</v>
       </c>
@@ -4672,7 +4674,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>185</v>
       </c>
@@ -4709,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="F188">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4729,7 +4731,7 @@
         <v>5</v>
       </c>
       <c r="F189">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4749,7 +4751,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4769,7 +4771,7 @@
         <v>15</v>
       </c>
       <c r="F191">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4789,10 +4791,10 @@
         <v>20</v>
       </c>
       <c r="F192">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>191</v>
       </c>
@@ -4809,7 +4811,7 @@
         <v>25</v>
       </c>
       <c r="F193">
-        <v>1219</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -4912,7 +4914,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>197</v>
       </c>
@@ -5032,7 +5034,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>203</v>
       </c>
@@ -5152,7 +5154,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>209</v>
       </c>
@@ -5272,7 +5274,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>215</v>
       </c>
@@ -14669,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="F686">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -14689,7 +14691,7 @@
         <v>5</v>
       </c>
       <c r="F687">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -14709,7 +14711,7 @@
         <v>10</v>
       </c>
       <c r="F688">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -14729,7 +14731,7 @@
         <v>15</v>
       </c>
       <c r="F689">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -14749,7 +14751,7 @@
         <v>20</v>
       </c>
       <c r="F690">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -14769,7 +14771,7 @@
         <v>25</v>
       </c>
       <c r="F691">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16109,7 +16111,7 @@
         <v>1</v>
       </c>
       <c r="F758">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16129,7 +16131,7 @@
         <v>5</v>
       </c>
       <c r="F759">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16149,7 +16151,7 @@
         <v>10</v>
       </c>
       <c r="F760">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16169,7 +16171,7 @@
         <v>15</v>
       </c>
       <c r="F761">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16189,7 +16191,7 @@
         <v>20</v>
       </c>
       <c r="F762">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16209,7 +16211,7 @@
         <v>25</v>
       </c>
       <c r="F763">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16229,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="F764">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16249,7 +16251,7 @@
         <v>5</v>
       </c>
       <c r="F765">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16269,7 +16271,7 @@
         <v>10</v>
       </c>
       <c r="F766">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16289,7 +16291,7 @@
         <v>15</v>
       </c>
       <c r="F767">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16309,7 +16311,7 @@
         <v>20</v>
       </c>
       <c r="F768">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -16329,7 +16331,7 @@
         <v>25</v>
       </c>
       <c r="F769">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17669,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="F836">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="837" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17689,7 +17691,7 @@
         <v>5</v>
       </c>
       <c r="F837">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="838" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17709,7 +17711,7 @@
         <v>10</v>
       </c>
       <c r="F838">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="839" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17729,7 +17731,7 @@
         <v>15</v>
       </c>
       <c r="F839">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="840" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17749,7 +17751,7 @@
         <v>20</v>
       </c>
       <c r="F840">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="841" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -17769,7 +17771,7 @@
         <v>25</v>
       </c>
       <c r="F841">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
@@ -18253,7 +18255,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F865" xr:uid="{014182E0-0F64-41E4-8B38-D14BA84013E9}">
+  <autoFilter ref="A1:F865" xr:uid="{03E296F0-887D-4CA4-B8F9-FCCD8573A670}">
     <filterColumn colId="1">
       <filters>
         <filter val="gsm"/>
@@ -18261,7 +18263,15 @@
     </filterColumn>
     <filterColumn colId="4">
       <filters>
+        <filter val="1"/>
         <filter val="25"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="1219"/>
+        <filter val="1240"/>
+        <filter val="1280"/>
       </filters>
     </filterColumn>
   </autoFilter>
